--- a/M-Project/M-Project_CED60/Docs/mcu설정.xlsx
+++ b/M-Project/M-Project_CED60/Docs/mcu설정.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\M-Project\M-Project_ES1\Docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\M-Project\M-Project_CED60\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D926F528-5B46-4BA1-A7B5-7633E53953F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{791B64DB-8872-4ADA-9333-933CE54F2CF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="45405" yWindow="6420" windowWidth="21600" windowHeight="11055" xr2:uid="{ADE28207-3863-4EB5-B970-EB500DB0CD83}"/>
+    <workbookView xWindow="71880" yWindow="10515" windowWidth="29040" windowHeight="15720" xr2:uid="{ADE28207-3863-4EB5-B970-EB500DB0CD83}"/>
   </bookViews>
   <sheets>
     <sheet name="pinmap" sheetId="1" r:id="rId1"/>
@@ -1206,26 +1206,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F737D1BC-587A-483A-B6AB-43AEC392E050}">
   <dimension ref="B2:T38"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.5625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.3125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="7.3125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.1875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.3125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="2.5625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="8.3125" style="1" customWidth="1"/>
-    <col min="8" max="9" width="6.6875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.0625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.0625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.58203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.33203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="2.58203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="8.33203125" style="1" customWidth="1"/>
+    <col min="8" max="9" width="6.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.08203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.08203125" style="1" customWidth="1"/>
     <col min="12" max="12" width="9" style="1"/>
-    <col min="13" max="14" width="9.5625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="9.58203125" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="18" width="9" style="1"/>
     <col min="19" max="19" width="9.5" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:20" x14ac:dyDescent="0.6">
+    <row r="2" spans="2:20" x14ac:dyDescent="0.45">
       <c r="C2" s="10" t="s">
         <v>88</v>
       </c>
@@ -1242,7 +1242,7 @@
       <c r="S2" s="10"/>
       <c r="T2" s="10"/>
     </row>
-    <row r="3" spans="2:20" x14ac:dyDescent="0.6">
+    <row r="3" spans="2:20" x14ac:dyDescent="0.45">
       <c r="C3" s="1" t="s">
         <v>0</v>
       </c>
@@ -1271,7 +1271,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="4" spans="2:20" x14ac:dyDescent="0.6">
+    <row r="4" spans="2:20" x14ac:dyDescent="0.45">
       <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
@@ -1291,7 +1291,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="2:20" x14ac:dyDescent="0.6">
+    <row r="5" spans="2:20" x14ac:dyDescent="0.45">
       <c r="C5" s="1" t="s">
         <v>2</v>
       </c>
@@ -1311,7 +1311,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="2:20" x14ac:dyDescent="0.6">
+    <row r="6" spans="2:20" x14ac:dyDescent="0.45">
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
@@ -1331,7 +1331,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="2:20" x14ac:dyDescent="0.6">
+    <row r="7" spans="2:20" x14ac:dyDescent="0.45">
       <c r="C7" s="1" t="s">
         <v>90</v>
       </c>
@@ -1351,7 +1351,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="2:20" x14ac:dyDescent="0.6">
+    <row r="8" spans="2:20" x14ac:dyDescent="0.45">
       <c r="C8" s="1" t="s">
         <v>91</v>
       </c>
@@ -1374,7 +1374,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="2:20" x14ac:dyDescent="0.6">
+    <row r="9" spans="2:20" x14ac:dyDescent="0.45">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1394,7 +1394,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="2:20" x14ac:dyDescent="0.6">
+    <row r="10" spans="2:20" x14ac:dyDescent="0.45">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1416,7 +1416,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="2:20" x14ac:dyDescent="0.6">
+    <row r="11" spans="2:20" x14ac:dyDescent="0.45">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1438,7 +1438,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="2:20" x14ac:dyDescent="0.6">
+    <row r="12" spans="2:20" x14ac:dyDescent="0.45">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1458,7 +1458,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="2:20" x14ac:dyDescent="0.6">
+    <row r="13" spans="2:20" x14ac:dyDescent="0.45">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1478,7 +1478,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="2:20" x14ac:dyDescent="0.6">
+    <row r="14" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B14" s="1" t="s">
         <v>164</v>
       </c>
@@ -1501,7 +1501,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="2:20" x14ac:dyDescent="0.6">
+    <row r="15" spans="2:20" x14ac:dyDescent="0.45">
       <c r="C15" s="1" t="s">
         <v>4</v>
       </c>
@@ -1521,7 +1521,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="2:20" x14ac:dyDescent="0.6">
+    <row r="16" spans="2:20" x14ac:dyDescent="0.45">
       <c r="C16" s="1" t="s">
         <v>4</v>
       </c>
@@ -1541,7 +1541,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.6">
+    <row r="17" spans="3:14" x14ac:dyDescent="0.45">
       <c r="C17" s="1" t="s">
         <v>4</v>
       </c>
@@ -1564,7 +1564,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.6">
+    <row r="18" spans="3:14" x14ac:dyDescent="0.45">
       <c r="C18" s="1" t="s">
         <v>11</v>
       </c>
@@ -1584,7 +1584,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.6">
+    <row r="19" spans="3:14" x14ac:dyDescent="0.45">
       <c r="C19" s="1" t="s">
         <v>12</v>
       </c>
@@ -1604,7 +1604,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.6">
+    <row r="20" spans="3:14" x14ac:dyDescent="0.45">
       <c r="C20" s="1" t="s">
         <v>13</v>
       </c>
@@ -1624,7 +1624,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.6">
+    <row r="21" spans="3:14" x14ac:dyDescent="0.45">
       <c r="C21" s="1" t="s">
         <v>14</v>
       </c>
@@ -1644,7 +1644,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.6">
+    <row r="22" spans="3:14" x14ac:dyDescent="0.45">
       <c r="C22" s="1" t="s">
         <v>93</v>
       </c>
@@ -1664,7 +1664,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.6">
+    <row r="23" spans="3:14" x14ac:dyDescent="0.45">
       <c r="C23" s="1" t="s">
         <v>94</v>
       </c>
@@ -1684,7 +1684,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.6">
+    <row r="24" spans="3:14" x14ac:dyDescent="0.45">
       <c r="C24" s="1" t="s">
         <v>95</v>
       </c>
@@ -1704,7 +1704,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.6">
+    <row r="25" spans="3:14" x14ac:dyDescent="0.45">
       <c r="C25" s="1" t="s">
         <v>96</v>
       </c>
@@ -1724,7 +1724,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.6">
+    <row r="26" spans="3:14" x14ac:dyDescent="0.45">
       <c r="C26" s="1" t="s">
         <v>97</v>
       </c>
@@ -1744,7 +1744,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.6">
+    <row r="27" spans="3:14" x14ac:dyDescent="0.45">
       <c r="C27" s="1" t="s">
         <v>8</v>
       </c>
@@ -1764,7 +1764,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.6">
+    <row r="28" spans="3:14" x14ac:dyDescent="0.45">
       <c r="C28" s="1" t="s">
         <v>92</v>
       </c>
@@ -1787,7 +1787,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.6">
+    <row r="29" spans="3:14" x14ac:dyDescent="0.45">
       <c r="C29" s="1" t="s">
         <v>98</v>
       </c>
@@ -1807,7 +1807,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.6">
+    <row r="30" spans="3:14" x14ac:dyDescent="0.45">
       <c r="C30" s="1" t="s">
         <v>99</v>
       </c>
@@ -1827,7 +1827,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.6">
+    <row r="31" spans="3:14" x14ac:dyDescent="0.45">
       <c r="C31" s="1" t="s">
         <v>100</v>
       </c>
@@ -1847,7 +1847,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.6">
+    <row r="32" spans="3:14" x14ac:dyDescent="0.45">
       <c r="C32" s="1" t="s">
         <v>101</v>
       </c>
@@ -1867,7 +1867,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="33" spans="3:14" x14ac:dyDescent="0.6">
+    <row r="33" spans="3:14" x14ac:dyDescent="0.45">
       <c r="C33" s="1" t="s">
         <v>102</v>
       </c>
@@ -1887,7 +1887,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="34" spans="3:14" x14ac:dyDescent="0.6">
+    <row r="34" spans="3:14" x14ac:dyDescent="0.45">
       <c r="C34" s="1" t="s">
         <v>103</v>
       </c>
@@ -1907,7 +1907,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="3:14" x14ac:dyDescent="0.6">
+    <row r="35" spans="3:14" x14ac:dyDescent="0.45">
       <c r="C35" s="1" t="s">
         <v>104</v>
       </c>
@@ -1927,7 +1927,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="3:14" x14ac:dyDescent="0.6">
+    <row r="36" spans="3:14" x14ac:dyDescent="0.45">
       <c r="C36" s="1" t="s">
         <v>105</v>
       </c>
@@ -1947,7 +1947,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="3:14" x14ac:dyDescent="0.6">
+    <row r="37" spans="3:14" x14ac:dyDescent="0.45">
       <c r="C37" s="1" t="s">
         <v>106</v>
       </c>
@@ -1967,7 +1967,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="3:14" x14ac:dyDescent="0.6">
+    <row r="38" spans="3:14" x14ac:dyDescent="0.45">
       <c r="C38" s="1" t="s">
         <v>8</v>
       </c>
@@ -2020,17 +2020,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D65EF832-A945-4D56-83E7-465E3AF1A3A1}">
   <dimension ref="B2:R17"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.5625" customWidth="1"/>
-    <col min="2" max="2" width="9.9375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.6875" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="10.5625" bestFit="1" customWidth="1"/>
-    <col min="10" max="13" width="11.6875" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="10.5625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.58203125" customWidth="1"/>
+    <col min="2" max="2" width="9.9140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="9" width="10.58203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="13" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="10.58203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:18" x14ac:dyDescent="0.6">
+    <row r="2" spans="2:18" x14ac:dyDescent="0.45">
       <c r="C2" t="s">
         <v>85</v>
       </c>
@@ -2038,7 +2038,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="3" spans="2:18" x14ac:dyDescent="0.6">
+    <row r="3" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B3" s="5" t="s">
         <v>83</v>
       </c>
@@ -2050,7 +2050,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="4" spans="2:18" x14ac:dyDescent="0.6">
+    <row r="4" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B4" s="5" t="s">
         <v>70</v>
       </c>
@@ -2064,7 +2064,7 @@
       <c r="Q4" s="4"/>
       <c r="R4" s="4"/>
     </row>
-    <row r="6" spans="2:18" x14ac:dyDescent="0.6">
+    <row r="6" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B6" s="5"/>
       <c r="C6" s="5" t="s">
         <v>61</v>
@@ -2109,7 +2109,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="7" spans="2:18" x14ac:dyDescent="0.6">
+    <row r="7" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B7" s="5" t="s">
         <v>69</v>
       </c>
@@ -2156,7 +2156,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="2:18" x14ac:dyDescent="0.6">
+    <row r="8" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B8" s="5" t="s">
         <v>84</v>
       </c>
@@ -2203,7 +2203,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="2:18" x14ac:dyDescent="0.6">
+    <row r="9" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B9" s="5" t="s">
         <v>87</v>
       </c>
@@ -2211,7 +2211,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="10" spans="2:18" x14ac:dyDescent="0.6">
+    <row r="10" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B10" s="5" t="s">
         <v>82</v>
       </c>
@@ -2272,7 +2272,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.6">
+    <row r="11" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B11" s="5" t="s">
         <v>71</v>
       </c>
@@ -2319,7 +2319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.6">
+    <row r="12" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B12" s="5" t="s">
         <v>72</v>
       </c>
@@ -2366,7 +2366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:18" x14ac:dyDescent="0.6">
+    <row r="13" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B13" s="5" t="s">
         <v>73</v>
       </c>
@@ -2427,7 +2427,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="14" spans="2:18" x14ac:dyDescent="0.6">
+    <row r="14" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B14" s="5" t="s">
         <v>74</v>
       </c>
@@ -2488,7 +2488,7 @@
         <v>108000</v>
       </c>
     </row>
-    <row r="15" spans="2:18" x14ac:dyDescent="0.6">
+    <row r="15" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B15" s="5" t="s">
         <v>75</v>
       </c>
@@ -2549,7 +2549,7 @@
         <v>108000000</v>
       </c>
     </row>
-    <row r="17" spans="3:3" x14ac:dyDescent="0.6">
+    <row r="17" spans="3:3" x14ac:dyDescent="0.45">
       <c r="C17" s="9"/>
     </row>
   </sheetData>
@@ -2562,7 +2562,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0B61A7B-3973-4596-B7CB-0BE6A561236A}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
